--- a/data/base/Backlog_39.xlsx
+++ b/data/base/Backlog_39.xlsx
@@ -8,20 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B3D7B88-03F7-4952-A0BA-0DC2074BF54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37953FE5-0F97-461F-8904-AF400493C8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{89F2F7A2-5DE5-41CE-9AA0-70F15A85C20D}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{89F2F7A2-5DE5-41CE-9AA0-70F15A85C20D}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="1" r:id="rId1"/>
     <sheet name="ITI" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="29">
   <si>
     <t>Status</t>
   </si>
@@ -105,6 +108,9 @@
   </si>
   <si>
     <t>Willian Rios</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -629,7 +635,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -637,22 +643,23 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1033,17 +1040,18 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="3"/>
-    <col min="11" max="11" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="8"/>
+    <col min="11" max="11" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1082,177 +1090,177 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="6">
-        <v>39</v>
-      </c>
-      <c r="E2" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F2" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="C2" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="5">
+        <v>39</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G2" s="5">
         <v>25463</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>46286.714861111112</v>
       </c>
-      <c r="I2" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J2" s="6" t="s">
+      <c r="I2" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="6">
-        <v>39</v>
-      </c>
-      <c r="E3" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F3" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="C3" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="5">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G3" s="5">
         <v>25528</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>46287.557430555556</v>
       </c>
-      <c r="I3" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="I3" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="6">
-        <v>39</v>
-      </c>
-      <c r="E4" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F4" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="C4" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="5">
+        <v>39</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G4" s="5">
         <v>25951</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>46293.668715277781</v>
       </c>
-      <c r="I4" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J4" s="6" t="s">
+      <c r="I4" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="6">
-        <v>39</v>
-      </c>
-      <c r="E5" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F5" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="C5" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="5">
+        <v>39</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G5" s="5">
         <v>25985</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>46294.376516203702</v>
       </c>
-      <c r="I5" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J5" s="6" t="s">
+      <c r="I5" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="6">
-        <v>39</v>
-      </c>
-      <c r="E6" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F6" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="C6" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="5">
+        <v>39</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G6" s="5">
         <v>26080</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>46295.462407407409</v>
       </c>
-      <c r="I6" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="I6" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1266,17 +1274,18 @@
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1315,675 +1324,680 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="5">
+        <v>39</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G2" s="5">
+        <v>25827</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46290.64403935185</v>
+      </c>
+      <c r="I2" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="5">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G3" s="5">
+        <v>25719</v>
+      </c>
+      <c r="H3" s="7">
+        <v>46289.574537037035</v>
+      </c>
+      <c r="I3" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="5">
+        <v>39</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G4" s="5">
+        <v>25887</v>
+      </c>
+      <c r="H4" s="7">
+        <v>46293.373622685183</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="5">
+        <v>39</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G5" s="5">
+        <v>25892</v>
+      </c>
+      <c r="H5" s="7">
+        <v>46293.401770833334</v>
+      </c>
+      <c r="I5" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="5">
+        <v>39</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G6" s="5">
+        <v>25993</v>
+      </c>
+      <c r="H6" s="7">
+        <v>46294.410069444442</v>
+      </c>
+      <c r="I6" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="5">
+        <v>39</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G7" s="5">
+        <v>26026</v>
+      </c>
+      <c r="H7" s="7">
+        <v>46294.644375000003</v>
+      </c>
+      <c r="I7" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="5">
+        <v>39</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G8" s="5">
+        <v>26102</v>
+      </c>
+      <c r="H8" s="7">
+        <v>46295.588067129633</v>
+      </c>
+      <c r="I8" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="5">
+        <v>39</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G9" s="5">
+        <v>24939</v>
+      </c>
+      <c r="H9" s="7">
+        <v>46279.395868055559</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="5">
+        <v>39</v>
+      </c>
+      <c r="E10" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G10" s="5">
+        <v>25955</v>
+      </c>
+      <c r="H10" s="7">
+        <v>46293.680393518516</v>
+      </c>
+      <c r="I10" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="5">
+        <v>39</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G11" s="5">
+        <v>24809</v>
+      </c>
+      <c r="H11" s="7">
+        <v>46275.733888888892</v>
+      </c>
+      <c r="I11" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="5">
+        <v>39</v>
+      </c>
+      <c r="E12" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G12" s="5">
+        <v>25818</v>
+      </c>
+      <c r="H12" s="7">
+        <v>46290.623692129629</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="6">
-        <v>39</v>
-      </c>
-      <c r="E2" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F2" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="C13" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="5">
+        <v>39</v>
+      </c>
+      <c r="E13" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G13" s="5">
         <v>22680</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H13" s="7">
         <v>46241.559837962966</v>
       </c>
-      <c r="I2" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J2" s="6" t="s">
+      <c r="I13" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="6">
-        <v>39</v>
-      </c>
-      <c r="E3" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F3" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G3" s="6">
-        <v>24809</v>
-      </c>
-      <c r="H3" s="8">
-        <v>46275.733888888892</v>
-      </c>
-      <c r="I3" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="5">
+        <v>39</v>
+      </c>
+      <c r="E14" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G14" s="5">
+        <v>25406</v>
+      </c>
+      <c r="H14" s="7">
+        <v>46286.40253472222</v>
+      </c>
+      <c r="I14" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="5">
+        <v>39</v>
+      </c>
+      <c r="E15" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G15" s="5">
+        <v>25561</v>
+      </c>
+      <c r="H15" s="7">
+        <v>46287.710196759261</v>
+      </c>
+      <c r="I15" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="6">
-        <v>39</v>
-      </c>
-      <c r="E4" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F4" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G4" s="6">
-        <v>24939</v>
-      </c>
-      <c r="H4" s="8">
-        <v>46279.395868055559</v>
-      </c>
-      <c r="I4" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="B16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="5">
+        <v>39</v>
+      </c>
+      <c r="E16" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G16" s="5">
+        <v>25956</v>
+      </c>
+      <c r="H16" s="7">
+        <v>46293.681273148148</v>
+      </c>
+      <c r="I16" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="6">
-        <v>39</v>
-      </c>
-      <c r="E5" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F5" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G5" s="6">
-        <v>25406</v>
-      </c>
-      <c r="H5" s="8">
-        <v>46286.40253472222</v>
-      </c>
-      <c r="I5" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="C17" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="5">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G17" s="5">
+        <v>26012</v>
+      </c>
+      <c r="H17" s="7">
+        <v>46294.535671296297</v>
+      </c>
+      <c r="I17" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="6">
-        <v>39</v>
-      </c>
-      <c r="E6" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F6" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G6" s="6">
-        <v>25561</v>
-      </c>
-      <c r="H6" s="8">
-        <v>46287.710196759261</v>
-      </c>
-      <c r="I6" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="B18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="5">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G18" s="5">
+        <v>25793</v>
+      </c>
+      <c r="H18" s="7">
+        <v>46290.412638888891</v>
+      </c>
+      <c r="I18" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="6">
-        <v>39</v>
-      </c>
-      <c r="E7" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F7" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G7" s="6">
-        <v>25719</v>
-      </c>
-      <c r="H7" s="8">
-        <v>46289.574537037035</v>
-      </c>
-      <c r="I7" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="5">
+        <v>39</v>
+      </c>
+      <c r="E19" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F19" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G19" s="5">
+        <v>25911</v>
+      </c>
+      <c r="H19" s="7">
+        <v>46293.512708333335</v>
+      </c>
+      <c r="I19" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="6">
-        <v>39</v>
-      </c>
-      <c r="E8" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F8" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G8" s="6">
-        <v>25793</v>
-      </c>
-      <c r="H8" s="8">
-        <v>46290.412638888891</v>
-      </c>
-      <c r="I8" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="4" t="s">
+      <c r="B20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="5">
+        <v>39</v>
+      </c>
+      <c r="E20" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46304</v>
+      </c>
+      <c r="G20" s="5">
+        <v>25869</v>
+      </c>
+      <c r="H20" s="7">
+        <v>46293.301064814812</v>
+      </c>
+      <c r="I20" s="6">
+        <v>46300</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="6">
-        <v>39</v>
-      </c>
-      <c r="E9" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F9" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G9" s="6">
-        <v>25818</v>
-      </c>
-      <c r="H9" s="8">
-        <v>46290.623692129629</v>
-      </c>
-      <c r="I9" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="6">
-        <v>39</v>
-      </c>
-      <c r="E10" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F10" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G10" s="6">
-        <v>25827</v>
-      </c>
-      <c r="H10" s="8">
-        <v>46290.64403935185</v>
-      </c>
-      <c r="I10" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="6">
-        <v>39</v>
-      </c>
-      <c r="E11" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F11" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G11" s="6">
-        <v>25869</v>
-      </c>
-      <c r="H11" s="8">
-        <v>46293.301064814812</v>
-      </c>
-      <c r="I11" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="6">
-        <v>39</v>
-      </c>
-      <c r="E12" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F12" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G12" s="6">
-        <v>25887</v>
-      </c>
-      <c r="H12" s="8">
-        <v>46293.373622685183</v>
-      </c>
-      <c r="I12" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="6">
-        <v>39</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F13" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G13" s="6">
-        <v>25892</v>
-      </c>
-      <c r="H13" s="8">
-        <v>46293.401770833334</v>
-      </c>
-      <c r="I13" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="6">
-        <v>39</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F14" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G14" s="6">
-        <v>25911</v>
-      </c>
-      <c r="H14" s="8">
-        <v>46293.512708333335</v>
-      </c>
-      <c r="I14" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="6">
-        <v>39</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F15" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G15" s="6">
-        <v>25955</v>
-      </c>
-      <c r="H15" s="8">
-        <v>46293.680393518516</v>
-      </c>
-      <c r="I15" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="6">
-        <v>39</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F16" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G16" s="6">
-        <v>25956</v>
-      </c>
-      <c r="H16" s="8">
-        <v>46293.681273148148</v>
-      </c>
-      <c r="I16" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="6">
-        <v>39</v>
-      </c>
-      <c r="E17" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F17" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G17" s="6">
-        <v>25993</v>
-      </c>
-      <c r="H17" s="8">
-        <v>46294.410069444442</v>
-      </c>
-      <c r="I17" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="6">
-        <v>39</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F18" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G18" s="6">
-        <v>26012</v>
-      </c>
-      <c r="H18" s="8">
-        <v>46294.535671296297</v>
-      </c>
-      <c r="I18" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="6">
-        <v>39</v>
-      </c>
-      <c r="E19" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F19" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G19" s="6">
-        <v>26026</v>
-      </c>
-      <c r="H19" s="8">
-        <v>46294.644375000003</v>
-      </c>
-      <c r="I19" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="6">
-        <v>39</v>
-      </c>
-      <c r="E20" s="7">
-        <v>46300</v>
-      </c>
-      <c r="F20" s="7">
-        <v>46304</v>
-      </c>
-      <c r="G20" s="6">
-        <v>26102</v>
-      </c>
-      <c r="H20" s="8">
-        <v>46295.588067129633</v>
-      </c>
-      <c r="I20" s="7">
-        <v>46300</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{46D4DF17-69FE-405F-A5DF-D4AC40352926}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K20">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>